--- a/data/UOL_Community_Engagement.xlsx
+++ b/data/UOL_Community_Engagement.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="1" r:id="R6bdc611c80174e6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="R53e6b970e44548ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Engagement" sheetId="1" r:id="R71a3951efe004d5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" r:id="Rf51665a281594dbf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -501,7 +501,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="N4" s="7" t="str">
-        <x:v>S.A.F.E Society</x:v>
+        <x:v>SAFE Society</x:v>
       </x:c>
       <x:c r="O4" s="7" t="str">
         <x:v>Yes</x:v>
@@ -779,7 +779,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e3022eb86b94496"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b1fd97650e94f4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
